--- a/dotnet/tests/corpus/features/sheet-row-height-break.xlsx
+++ b/dotnet/tests/corpus/features/sheet-row-height-break.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t xml:space="preserve">Alpha
 Bravo
@@ -27,6 +27,9 @@
   <si>
     <t xml:space="preserve">Alpha
 Bravo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha</t>
   </si>
 </sst>
 </file>
@@ -94,6 +97,11 @@
         <v>3</v>
       </c>
     </row>
+    <row r="5" ht="15" spans="1:1">
+      <c r="A5" s="0" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>